--- a/backend/data/serials.xlsx
+++ b/backend/data/serials.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11055"/>
+    <workbookView windowWidth="28800" windowHeight="12510"/>
   </bookViews>
   <sheets>
     <sheet name="A" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="472">
   <si>
     <t>序号</t>
   </si>
@@ -46,31 +46,1405 @@
     <t>备注</t>
   </si>
   <si>
+    <t>TC01WBD202509091046041730603</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043907336</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043172612</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043367954</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046049328537</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043923227</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046042303963</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044314452</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040397283</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046046649504</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046041454288</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040584011</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044306460</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046049570806</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040677469</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046048552610</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043320496</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046041205049</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040348984</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044658013</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046045523995</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046049005317</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046045787677</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046041249537</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046048530589</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046046404833</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043817124</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046041162799</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046042740837</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043812393</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040706355</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046042036221</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046049504261</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044759035</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046042003243</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046047696992</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046041125248</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046041349855</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046042807712</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046046925172</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040325958</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046046530226</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044108048</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044027494</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046048910916</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046048048837</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046043744887</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046045283168</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046049324345</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046042302616</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046042845523</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044068995</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044613889</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040506033</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046048739974</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046049231124</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046044758538</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529524033</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525152356</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046045838926</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299139852</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299041318</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294635218</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622291004546</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622291967766</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292380718</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622291564929</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295130046</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295055659</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298323489</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622290346997</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296017392</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295537741</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295325442</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295597191</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293863213</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294153946</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292422756</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295321895</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299020820</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293174419</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294299468</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299033361</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296216968</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294724478</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296437058</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292943789</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292350985</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622297126703</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622290860238</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298340845</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294921064</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294812532</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299930657</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299769657</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293109654</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299295099</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296332432</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622290303562</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299304536</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622297595171</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296953282</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299793991</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299994918</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295738276</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622297667561</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299041916</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293718012</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130526683647</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130528356071</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525949975</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130520306431</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525534094</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522559935</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525666248</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130528857015</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523322355</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130521977922</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522261200</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525916528</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525540278</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130524725004</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130526501619</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527029656</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529987934</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130528100768</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523661078</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523991913</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130521559840</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130521769903</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529522595</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522166132</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529513884</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529229567</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525563265</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529690324</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529074832</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522294584</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130520493881</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523855800</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130526523479</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130520414115</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130520566010</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529457335</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525713805</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522172437</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130526325018</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529897043</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130528701576</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130524174846</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527935193</t>
+  </si>
+  <si>
+    <t>TC01WBD202509091046040823534</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527900943</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130524367977</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523981881</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130526891732</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527383939</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295557389</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468439325</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468040996</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461780954</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466519672</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462450850</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462884561</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463755091</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469922117</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464232824</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469741300</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469086180</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461691367</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468914618</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461231028</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462211468</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129467768679</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463855773</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460445803</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462180024</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463909486</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461474990</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464743415</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465907006</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129467609140</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462556718</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466283117</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465658006</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466074451</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462839125</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464298400</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468868394</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468904381</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129467544307</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469747476</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129467605461</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129467652634</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460875388</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461919982</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460209132</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469674050</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466005483</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463262626</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469387826</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460132086</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465974626</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463724859</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468542280</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465720511</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468377048</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465640123</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129467304589</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464743785</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460722639</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469443775</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527543888</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461641385</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460008380</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462153881</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469810228</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464868726</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469235720</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129467748650</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468793024</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464469312</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461899393</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462710110</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468626613</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463346489</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129468753823</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465313651</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469038407</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469904006</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466607534</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466799392</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463192355</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461927402</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461050239</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465263186</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460510143</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464463591</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463696266</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464843619</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129469048761</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464095546</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464752772</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464587046</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463485761</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129463613556</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129464514214</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465495991</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129461183377</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465018406</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466433590</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466529188</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129460121390</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462940921</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466933867</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129465879870</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129466387729</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021129462532485</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525216213</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523219366</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529321058</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529470847</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522878716</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525907205</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527761941</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130526297074</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522398239</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130520563116</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130528811368</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522968187</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130521465867</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523931478</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130520229210</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525047380</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130524830265</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525696996</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130526357041</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529654739</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525656799</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529673813</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130521376486</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525011393</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130524085075</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523547075</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525386853</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527583123</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527464434</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130528220570</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525844914</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522861612</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527677914</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527084096</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529145558</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527454874</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130522719210</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527039411</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130523095084</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130527542844</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130524067875</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130528956365</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525185643</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130529849507</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525690221</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130525282214</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130520651173</t>
+  </si>
+  <si>
+    <t>TC01WBD202509021130524490110</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299312648</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298507217</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476639170</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473445437</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131475850960</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470033737</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471920074</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473102903</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474232747</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473074683</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478027057</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473282824</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474757604</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476374823</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472918137</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472948853</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477513017</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131475940969</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470556968</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472365632</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472577620</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470268709</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476061808</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131475897508</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477645533</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473639968</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479192421</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473262885</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474205964</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471987665</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477603479</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474213758</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477233788</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472084787</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474710880</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476067675</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479299746</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470267061</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470372828</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474728979</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477196148</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470921977</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476902509</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477434334</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473446771</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472045926</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476895755</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478554334</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479815839</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470374272</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470771192</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470766269</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473455233</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476050967</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479940188</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471399934</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478462191</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477724175</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478338321</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470742264</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471997158</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471898075</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477658935</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471841616</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473840053</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479147946</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131470396261</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474517491</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477893706</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478812180</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478750857</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474651335</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473583949</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131475875097</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472555549</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478378211</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471546531</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477622501</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131475787814</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473827160</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476610479</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473916774</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479179686</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131473271837</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131475462930</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471620939</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476156476</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479441082</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131477647778</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131474617861</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478250543</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472100771</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472054139</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479381500</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131475199740</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476000304</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476525470</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131478250136</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131471602760</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131479464561</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131476543810</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211131472765704</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294293277</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298884040</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294083170</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298496875</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293887097</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296754508</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296322357</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299950238</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296905354</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295475835</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622291215973</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298767653</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293176065</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622290495998</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298983255</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622290096444</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292357273</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292194826</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294659649</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292644662</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299843088</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298847603</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293667134</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298418774</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622291930791</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299572865</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294738765</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295734154</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622297873758</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293243262</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296430499</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292728303</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298880966</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622291275007</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293815559</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622296466399</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292333743</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622292760572</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622297611509</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293514751</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622297274682</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293752198</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622294837867</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299372668</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622298463373</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622293651097</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622295088030</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299222074</t>
+  </si>
+  <si>
+    <t>TC01WBD202508211622299161846</t>
+  </si>
+  <si>
+    <t>TC01WBD202508201455290543047</t>
+  </si>
+  <si>
+    <t>TC01WBD202508111656476931982</t>
+  </si>
+  <si>
+    <t>未烧录</t>
+  </si>
+  <si>
+    <t>TC01WBD202508111656479962939</t>
+  </si>
+  <si>
+    <t>2025-08-11 16:56:47</t>
+  </si>
+  <si>
+    <t>TC01WBD202508111656471609154</t>
+  </si>
+  <si>
+    <t>TC01WBD202508111656474890886</t>
+  </si>
+  <si>
+    <t>TC01WBD202508111656479998041</t>
+  </si>
+  <si>
     <t>TC01WBD202508111656476931981</t>
-  </si>
-  <si>
-    <t>未烧录</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TC01WBD202508111656479962939</t>
-  </si>
-  <si>
-    <t>2025-08-11 16:56:47</t>
-  </si>
-  <si>
-    <t>TC01WBD202508111656471609154</t>
-  </si>
-  <si>
-    <t>TC01WBD202508111656474890886</t>
-  </si>
-  <si>
-    <t>TC01WBD202508111656479998041</t>
-  </si>
-  <si>
-    <t>TC01WBD202508111656476931982</t>
   </si>
 </sst>
 </file>
@@ -85,7 +1459,7 @@
   </numFmts>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -691,9 +2065,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -746,7 +2119,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -830,6 +2203,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -864,6 +2238,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -898,20 +2273,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1033,19 +2404,54 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
-  <cols>
-    <col min="2" max="2" width="40.875" customWidth="1"/>
-    <col min="3" max="3" width="39.625" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E459"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1068,90 +2474,2328 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>45880.706099537</v>
-      </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>45880.706099537</v>
-      </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
       <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3">
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3">
+      <c r="C39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3">
+      <c r="C41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3">
+      <c r="C43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3">
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3">
+      <c r="C45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3">
+      <c r="C46" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3">
+      <c r="C47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3">
+      <c r="C51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3">
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3">
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3">
+      <c r="C54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3">
+      <c r="C55" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3">
+      <c r="C56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3">
+      <c r="C57" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3">
+      <c r="C58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3">
+      <c r="C61" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3">
+      <c r="C62" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3">
+      <c r="C63" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3">
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3">
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3">
+      <c r="C66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3">
+      <c r="C67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3">
+      <c r="C68" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3">
+      <c r="C69" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3">
+      <c r="C70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3">
+      <c r="C71" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3">
+      <c r="C72" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3">
+      <c r="C73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3">
+      <c r="C74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3">
+      <c r="C75" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3">
+      <c r="C76" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3">
+      <c r="C77" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3">
+      <c r="C78" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3">
+      <c r="C79" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3">
+      <c r="C80" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
+      <c r="C81" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
+      <c r="C82" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3">
+      <c r="C83" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3">
+      <c r="C84" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3">
+      <c r="C85" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3">
+      <c r="C86" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3">
+      <c r="C90" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3">
+      <c r="C91" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
+      <c r="C92" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3">
+      <c r="C93" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3">
+      <c r="C94" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3">
+      <c r="C95" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3">
+      <c r="C96" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3">
+      <c r="C97" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3">
+      <c r="C98" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3">
+      <c r="C99" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3">
+      <c r="C100" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3">
+      <c r="C101" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="102" spans="3:3">
+      <c r="C102" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="103" spans="3:3">
+      <c r="C103" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3">
+      <c r="C104" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="3:3">
+      <c r="C105" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="106" spans="3:3">
+      <c r="C106" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="107" spans="3:3">
+      <c r="C107" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="108" spans="3:3">
+      <c r="C108" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="109" spans="3:3">
+      <c r="C109" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="3:3">
+      <c r="C110" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="111" spans="3:3">
+      <c r="C111" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="112" spans="3:3">
+      <c r="C112" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="113" spans="3:3">
+      <c r="C113" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3">
+      <c r="C114" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3">
+      <c r="C115" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3">
+      <c r="C116" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3">
+      <c r="C117" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3">
+      <c r="C118" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3">
+      <c r="C119" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="120" spans="3:3">
+      <c r="C120" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="121" spans="3:3">
+      <c r="C121" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="122" spans="3:3">
+      <c r="C122" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="3:3">
+      <c r="C123" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3">
+      <c r="C124" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3">
+      <c r="C125" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3">
+      <c r="C126" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="127" spans="3:3">
+      <c r="C127" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="128" spans="3:3">
+      <c r="C128" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3">
+      <c r="C129" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="130" spans="3:3">
+      <c r="C130" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="131" spans="3:3">
+      <c r="C131" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="132" spans="3:3">
+      <c r="C132" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="133" spans="3:3">
+      <c r="C133" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="134" spans="3:3">
+      <c r="C134" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="135" spans="3:3">
+      <c r="C135" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="136" spans="3:3">
+      <c r="C136" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="137" spans="3:3">
+      <c r="C137" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="138" spans="3:3">
+      <c r="C138" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="139" spans="3:3">
+      <c r="C139" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="140" spans="3:3">
+      <c r="C140" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="141" spans="3:3">
+      <c r="C141" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="142" spans="3:3">
+      <c r="C142" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="143" spans="3:3">
+      <c r="C143" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="144" spans="3:3">
+      <c r="C144" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3">
+      <c r="C145" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3">
+      <c r="C146" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3">
+      <c r="C147" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3">
+      <c r="C148" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3">
+      <c r="C149" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3">
+      <c r="C150" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="151" spans="3:3">
+      <c r="C151" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3">
+      <c r="C152" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="153" spans="3:3">
+      <c r="C153" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="154" spans="3:3">
+      <c r="C154" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="155" spans="3:3">
+      <c r="C155" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="156" spans="3:3">
+      <c r="C156" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="157" spans="3:3">
+      <c r="C157" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3">
+      <c r="C158" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3">
+      <c r="C159" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="160" spans="3:3">
+      <c r="C160" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3">
+      <c r="C161" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="162" spans="3:3">
+      <c r="C162" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="163" spans="3:3">
+      <c r="C163" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="164" spans="3:3">
+      <c r="C164" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="165" spans="3:3">
+      <c r="C165" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="166" spans="3:3">
+      <c r="C166" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="167" spans="3:3">
+      <c r="C167" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="168" spans="3:3">
+      <c r="C168" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="169" spans="3:3">
+      <c r="C169" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="170" spans="3:3">
+      <c r="C170" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="171" spans="3:3">
+      <c r="C171" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="172" spans="3:3">
+      <c r="C172" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="173" spans="3:3">
+      <c r="C173" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="174" spans="3:3">
+      <c r="C174" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="175" spans="3:3">
+      <c r="C175" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="176" spans="3:3">
+      <c r="C176" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="177" spans="3:3">
+      <c r="C177" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="178" spans="3:3">
+      <c r="C178" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="179" spans="3:3">
+      <c r="C179" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="180" spans="3:3">
+      <c r="C180" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="181" spans="3:3">
+      <c r="C181" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="182" spans="3:3">
+      <c r="C182" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="183" spans="3:3">
+      <c r="C183" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="184" spans="3:3">
+      <c r="C184" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="185" spans="3:3">
+      <c r="C185" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="186" spans="3:3">
+      <c r="C186" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="187" spans="3:3">
+      <c r="C187" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="188" spans="3:3">
+      <c r="C188" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="189" spans="3:3">
+      <c r="C189" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="190" spans="3:3">
+      <c r="C190" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="191" spans="3:3">
+      <c r="C191" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="192" spans="3:3">
+      <c r="C192" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="193" spans="3:3">
+      <c r="C193" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="3:3">
+      <c r="C194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="3:3">
+      <c r="C195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="3:3">
+      <c r="C196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="3:3">
+      <c r="C197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="3:3">
+      <c r="C198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="3:3">
+      <c r="C199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="3:3">
+      <c r="C200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="3:3">
+      <c r="C201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="3:3">
+      <c r="C202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="3:3">
+      <c r="C203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="3:3">
+      <c r="C204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="3:3">
+      <c r="C205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="3:3">
+      <c r="C206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="3:3">
+      <c r="C207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="3:3">
+      <c r="C208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="3:3">
+      <c r="C209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="3:3">
+      <c r="C210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="3:3">
+      <c r="C211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="3:3">
+      <c r="C212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="3:3">
+      <c r="C213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="3:3">
+      <c r="C214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="3:3">
+      <c r="C215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="3:3">
+      <c r="C216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="3:3">
+      <c r="C217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="3:3">
+      <c r="C218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="3:3">
+      <c r="C219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="3:3">
+      <c r="C220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="3:3">
+      <c r="C221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="3:3">
+      <c r="C222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="3:3">
+      <c r="C223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="3:3">
+      <c r="C224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="3:3">
+      <c r="C225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="3:3">
+      <c r="C226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="3:3">
+      <c r="C227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="3:3">
+      <c r="C228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="3:3">
+      <c r="C229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="3:3">
+      <c r="C230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="3:3">
+      <c r="C231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="3:3">
+      <c r="C232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="3:3">
+      <c r="C233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="3:3">
+      <c r="C234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="3:3">
+      <c r="C235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="3:3">
+      <c r="C236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="3:3">
+      <c r="C237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="3:3">
+      <c r="C238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="3:3">
+      <c r="C239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="3:3">
+      <c r="C240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="3:3">
+      <c r="C241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="3:3">
+      <c r="C242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="3:3">
+      <c r="C243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="3:3">
+      <c r="C244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="3:3">
+      <c r="C245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="3:3">
+      <c r="C246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="3:3">
+      <c r="C247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="3:3">
+      <c r="C248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="3:3">
+      <c r="C249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="3:3">
+      <c r="C250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="3:3">
+      <c r="C251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="3:3">
+      <c r="C252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="3:3">
+      <c r="C253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="3:3">
+      <c r="C254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="3:3">
+      <c r="C255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="3:3">
+      <c r="C256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="3:3">
+      <c r="C257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="3:3">
+      <c r="C258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="3:3">
+      <c r="C259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="3:3">
+      <c r="C260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="3:3">
+      <c r="C261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="3:3">
+      <c r="C262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="3:3">
+      <c r="C263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="3:3">
+      <c r="C264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="3:3">
+      <c r="C265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="3:3">
+      <c r="C266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="3:3">
+      <c r="C267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="3:3">
+      <c r="C268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="3:3">
+      <c r="C269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="3:3">
+      <c r="C270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="3:3">
+      <c r="C271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="3:3">
+      <c r="C272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="3:3">
+      <c r="C273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="3:3">
+      <c r="C274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="3:3">
+      <c r="C275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="3:3">
+      <c r="C276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="3:3">
+      <c r="C277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="3:3">
+      <c r="C278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="3:3">
+      <c r="C279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="3:3">
+      <c r="C280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="3:3">
+      <c r="C281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="3:3">
+      <c r="C282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="3:3">
+      <c r="C283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="3:3">
+      <c r="C284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="3:3">
+      <c r="C285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="3:3">
+      <c r="C286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="3:3">
+      <c r="C287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="3:3">
+      <c r="C288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="3:3">
+      <c r="C289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="3:3">
+      <c r="C290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="3:3">
+      <c r="C291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="3:3">
+      <c r="C292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="3:3">
+      <c r="C293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="3:3">
+      <c r="C294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="3:3">
+      <c r="C295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="3:3">
+      <c r="C296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="3:3">
+      <c r="C297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="3:3">
+      <c r="C298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="3:3">
+      <c r="C299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="3:3">
+      <c r="C300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="3:3">
+      <c r="C301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="3:3">
+      <c r="C302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="3:3">
+      <c r="C303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="3:3">
+      <c r="C304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="3:3">
+      <c r="C305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="3:3">
+      <c r="C306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="3:3">
+      <c r="C307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="3:3">
+      <c r="C308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="3:3">
+      <c r="C309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="3:3">
+      <c r="C310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="3:3">
+      <c r="C311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="3:3">
+      <c r="C312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="3:3">
+      <c r="C313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="3:3">
+      <c r="C314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="3:3">
+      <c r="C315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="3:3">
+      <c r="C316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="3:3">
+      <c r="C317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="3:3">
+      <c r="C318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="3:3">
+      <c r="C319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="3:3">
+      <c r="C320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="3:3">
+      <c r="C321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="3:3">
+      <c r="C322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="3:3">
+      <c r="C323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="3:3">
+      <c r="C324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="3:3">
+      <c r="C325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="3:3">
+      <c r="C326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="3:3">
+      <c r="C327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="3:3">
+      <c r="C328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="3:3">
+      <c r="C329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="3:3">
+      <c r="C330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="3:3">
+      <c r="C331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="3:3">
+      <c r="C332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="3:3">
+      <c r="C333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="3:3">
+      <c r="C334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="3:3">
+      <c r="C335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="3:3">
+      <c r="C336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="3:3">
+      <c r="C337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="3:3">
+      <c r="C338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="3:3">
+      <c r="C339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="3:3">
+      <c r="C340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="3:3">
+      <c r="C341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="3:3">
+      <c r="C342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="3:3">
+      <c r="C343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="3:3">
+      <c r="C344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="3:3">
+      <c r="C345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="3:3">
+      <c r="C346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="3:3">
+      <c r="C347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="3:3">
+      <c r="C348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="3:3">
+      <c r="C349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="3:3">
+      <c r="C350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="3:3">
+      <c r="C351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="3:3">
+      <c r="C352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="3:3">
+      <c r="C353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="3:3">
+      <c r="C354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="3:3">
+      <c r="C355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="3:3">
+      <c r="C356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="3:3">
+      <c r="C357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="3:3">
+      <c r="C358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="3:3">
+      <c r="C359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="3:3">
+      <c r="C360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="3:3">
+      <c r="C361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="3:3">
+      <c r="C362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="3:3">
+      <c r="C363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="3:3">
+      <c r="C364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="3:3">
+      <c r="C365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="3:3">
+      <c r="C366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="3:3">
+      <c r="C367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="3:3">
+      <c r="C368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="3:3">
+      <c r="C369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="3:3">
+      <c r="C370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="3:3">
+      <c r="C371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="3:3">
+      <c r="C372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="3:3">
+      <c r="C373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="3:3">
+      <c r="C374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="3:3">
+      <c r="C375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="3:3">
+      <c r="C376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="3:3">
+      <c r="C377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="3:3">
+      <c r="C378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="3:3">
+      <c r="C379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="3:3">
+      <c r="C380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="3:3">
+      <c r="C381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="3:3">
+      <c r="C382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="3:3">
+      <c r="C383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="3:3">
+      <c r="C384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="3:3">
+      <c r="C385" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="386" spans="3:3">
+      <c r="C386" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="387" spans="3:3">
+      <c r="C387" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="388" spans="3:3">
+      <c r="C388" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="389" spans="3:3">
+      <c r="C389" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="390" spans="3:3">
+      <c r="C390" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="391" spans="3:3">
+      <c r="C391" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="392" spans="3:3">
+      <c r="C392" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="393" spans="3:3">
+      <c r="C393" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="394" spans="3:3">
+      <c r="C394" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="395" spans="3:3">
+      <c r="C395" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="396" spans="3:3">
+      <c r="C396" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="397" spans="3:3">
+      <c r="C397" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="398" spans="3:3">
+      <c r="C398" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="399" spans="3:3">
+      <c r="C399" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="400" spans="3:3">
+      <c r="C400" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="401" spans="3:3">
+      <c r="C401" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="402" spans="3:3">
+      <c r="C402" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="403" spans="3:3">
+      <c r="C403" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="404" spans="3:3">
+      <c r="C404" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="405" spans="3:3">
+      <c r="C405" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="406" spans="3:3">
+      <c r="C406" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="407" spans="3:3">
+      <c r="C407" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="408" spans="3:3">
+      <c r="C408" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="409" spans="3:3">
+      <c r="C409" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="410" spans="3:3">
+      <c r="C410" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="411" spans="3:3">
+      <c r="C411" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="412" spans="3:3">
+      <c r="C412" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="413" spans="3:3">
+      <c r="C413" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="414" spans="3:3">
+      <c r="C414" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="415" spans="3:3">
+      <c r="C415" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="416" spans="3:3">
+      <c r="C416" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="417" spans="3:3">
+      <c r="C417" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="418" spans="3:3">
+      <c r="C418" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="419" spans="3:3">
+      <c r="C419" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="420" spans="3:3">
+      <c r="C420" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="421" spans="3:3">
+      <c r="C421" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="422" spans="3:3">
+      <c r="C422" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="423" spans="3:3">
+      <c r="C423" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="424" spans="3:3">
+      <c r="C424" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="425" spans="3:3">
+      <c r="C425" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="426" spans="3:3">
+      <c r="C426" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="427" spans="3:3">
+      <c r="C427" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="428" spans="3:3">
+      <c r="C428" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="429" spans="3:3">
+      <c r="C429" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="430" spans="3:3">
+      <c r="C430" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="431" spans="3:3">
+      <c r="C431" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="432" spans="3:3">
+      <c r="C432" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="433" spans="3:3">
+      <c r="C433" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="434" spans="3:3">
+      <c r="C434" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="435" spans="3:3">
+      <c r="C435" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="436" spans="3:3">
+      <c r="C436" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="437" spans="3:3">
+      <c r="C437" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="438" spans="3:3">
+      <c r="C438" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="439" spans="3:3">
+      <c r="C439" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="440" spans="3:3">
+      <c r="C440" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="441" spans="3:3">
+      <c r="C441" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="442" spans="3:3">
+      <c r="C442" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="443" spans="3:3">
+      <c r="C443" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="444" spans="3:3">
+      <c r="C444" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="445" spans="3:3">
+      <c r="C445" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="446" spans="3:3">
+      <c r="C446" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="447" spans="3:3">
+      <c r="C447" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="448" spans="3:3">
+      <c r="C448" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="449" spans="3:3">
+      <c r="C449" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="450" spans="3:3">
+      <c r="C450" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="451" spans="3:3">
+      <c r="C451" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="452" spans="3:3">
+      <c r="C452" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="453" spans="3:3">
+      <c r="C453" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="454" spans="3:3">
+      <c r="C454" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="455" spans="3:3">
+      <c r="C455" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="456" spans="3:3">
+      <c r="C456" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="457" spans="3:3">
+      <c r="C457" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="458" spans="3:3">
+      <c r="C458" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="459" spans="3:3">
+      <c r="C459" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:E227 A228:C228 A229:E459" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1159,11 +4803,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
-  <cols>
-    <col min="2" max="2" width="40.875" customWidth="1"/>
-    <col min="3" max="3" width="39.625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1186,34 +4826,34 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>45880.706099537</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>464</v>
       </c>
       <c r="D2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>45880.706099537</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>466</v>
       </c>
       <c r="D3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1221,16 +4861,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>467</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>468</v>
       </c>
       <c r="D4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1238,46 +4878,49 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>467</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>469</v>
       </c>
       <c r="D5" t="s">
+        <v>465</v>
+      </c>
+      <c r="E5" t="s">
         <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>45880.706099537</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>470</v>
       </c>
       <c r="D6" t="s">
+        <v>465</v>
+      </c>
+      <c r="E6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>45880.706099537</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:E7" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1285,11 +4928,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
-  <cols>
-    <col min="2" max="2" width="40.875" customWidth="1"/>
-    <col min="3" max="3" width="39.625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1312,34 +4951,34 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>45880.706099537</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>471</v>
       </c>
       <c r="D2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>45880.706099537</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>466</v>
       </c>
       <c r="D3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1347,16 +4986,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>467</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>468</v>
       </c>
       <c r="D4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1364,16 +5003,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>467</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>469</v>
       </c>
       <c r="D5" t="s">
+        <v>465</v>
+      </c>
+      <c r="E5" t="s">
         <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1381,20 +5020,23 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>467</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>470</v>
       </c>
       <c r="D6" t="s">
+        <v>465</v>
+      </c>
+      <c r="E6" t="s">
         <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:E6" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>